--- a/DUS/DUS_YCOA_Mapping_Review_V5 copy.xlsx
+++ b/DUS/DUS_YCOA_Mapping_Review_V5 copy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\goeth\AppData\Local\Temp\claude\c--Users-goeth-desktop-SynchFolder-DUS\1b71695c-a8db-458e-ba42-89b089a2b98d\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://deudeloitte-my.sharepoint.com/personal/mgoethel_deloitte_de/Documents/Documents/Projekt/SynchFolder/DUS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B282F2-75DE-40DD-8F6E-4B26D829AF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{64B282F2-75DE-40DD-8F6E-4B26D829AF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31CA144F-385A-4831-8B81-8B81BDBBBDB7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5535" windowWidth="18360" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-14280" windowWidth="21840" windowHeight="37920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="1" r:id="rId1"/>
@@ -12092,7 +12092,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
@@ -12650,7 +12650,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N601"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -12710,7 +12710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="48" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -18270,7 +18270,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="131" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>573</v>
       </c>
@@ -20116,7 +20116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>733</v>
       </c>
@@ -23290,7 +23290,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="246" spans="1:14" ht="96" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>949</v>
       </c>
@@ -23336,7 +23336,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="247" spans="1:14" ht="84" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>954</v>
       </c>
@@ -23378,7 +23378,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="248" spans="1:14" ht="84" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>957</v>
       </c>
@@ -23420,7 +23420,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="249" spans="1:14" ht="84" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>959</v>
       </c>
@@ -23462,7 +23462,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="250" spans="1:14" ht="84" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>961</v>
       </c>
@@ -23504,7 +23504,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="251" spans="1:14" ht="84" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>963</v>
       </c>
@@ -23546,7 +23546,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="252" spans="1:14" ht="84" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>965</v>
       </c>
@@ -24584,7 +24584,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="24" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>1049</v>
       </c>
@@ -26820,7 +26820,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="328" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>1264</v>
       </c>
@@ -26944,7 +26944,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="331" spans="1:14" ht="48" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>1274</v>
       </c>
@@ -27404,7 +27404,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="342" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>1318</v>
       </c>
@@ -27448,7 +27448,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="343" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>1325</v>
       </c>
@@ -27488,7 +27488,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="344" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>1328</v>
       </c>
@@ -27528,7 +27528,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="345" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>1330</v>
       </c>
@@ -27568,7 +27568,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="346" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>1336</v>
       </c>
@@ -27612,7 +27612,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="347" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>1343</v>
       </c>
@@ -27656,7 +27656,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="348" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>1348</v>
       </c>
@@ -27696,7 +27696,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="349" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>1352</v>
       </c>
@@ -27736,7 +27736,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="350" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>1354</v>
       </c>
@@ -27810,7 +27810,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="352" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>1359</v>
       </c>
@@ -27854,7 +27854,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="353" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>1365</v>
       </c>
@@ -29294,7 +29294,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="387" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>1514</v>
       </c>
@@ -30108,7 +30108,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="407" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>1596</v>
       </c>
@@ -30934,7 +30934,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="427" spans="1:14" ht="24" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>1665</v>
       </c>
@@ -34270,7 +34270,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="506" spans="1:14" ht="24" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>1979</v>
       </c>
@@ -36532,7 +36532,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="558" spans="1:14" ht="24" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>2144</v>
       </c>
@@ -36572,7 +36572,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="559" spans="1:14" ht="24" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>2147</v>
       </c>
@@ -36612,7 +36612,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="560" spans="1:14" ht="24" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>2149</v>
       </c>
@@ -36740,7 +36740,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="563" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>2161</v>
       </c>
@@ -36780,7 +36780,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="564" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>2164</v>
       </c>
@@ -38474,7 +38474,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66" customWidth="1"/>
     <col min="2" max="7" width="15" customWidth="1"/>
@@ -39144,17 +39144,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B48:H48"/>
     <mergeCell ref="A58:H58"/>
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A55:H55"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="A54:H54"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B48:H48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -39171,7 +39171,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K91"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -39259,7 +39259,7 @@
         <v>773</v>
       </c>
       <c r="C6" s="4" t="str">
-        <f t="shared" ref="C6:C37" si="0">$C$3&amp;A6</f>
+        <f>$C$3&amp;A6</f>
         <v>41800000</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -39294,7 +39294,7 @@
         <v>776</v>
       </c>
       <c r="C7" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A7</f>
         <v>41800001</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -39329,7 +39329,7 @@
         <v>778</v>
       </c>
       <c r="C8" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A8</f>
         <v>41800002</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -39364,7 +39364,7 @@
         <v>788</v>
       </c>
       <c r="C9" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A9</f>
         <v>41800010</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -39399,7 +39399,7 @@
         <v>784</v>
       </c>
       <c r="C10" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A10</f>
         <v>41800020</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -39434,7 +39434,7 @@
         <v>795</v>
       </c>
       <c r="C11" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A11</f>
         <v>41800110</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -39469,7 +39469,7 @@
         <v>797</v>
       </c>
       <c r="C12" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A12</f>
         <v>41800111</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -39504,7 +39504,7 @@
         <v>767</v>
       </c>
       <c r="C13" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A13</f>
         <v>41800400</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -39539,7 +39539,7 @@
         <v>799</v>
       </c>
       <c r="C14" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A14</f>
         <v>41800420</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -39574,7 +39574,7 @@
         <v>801</v>
       </c>
       <c r="C15" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A15</f>
         <v>41800430</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -39609,7 +39609,7 @@
         <v>810</v>
       </c>
       <c r="C16" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A16</f>
         <v>41801000</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -39644,7 +39644,7 @@
         <v>813</v>
       </c>
       <c r="C17" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A17</f>
         <v>41810030</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -39679,7 +39679,7 @@
         <v>817</v>
       </c>
       <c r="C18" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A18</f>
         <v>41810032</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -39714,7 +39714,7 @@
         <v>786</v>
       </c>
       <c r="C19" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A19</f>
         <v>41810050</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -39749,7 +39749,7 @@
         <v>819</v>
       </c>
       <c r="C20" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A20</f>
         <v>41811010</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -39784,7 +39784,7 @@
         <v>822</v>
       </c>
       <c r="C21" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A21</f>
         <v>41811020</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -39819,7 +39819,7 @@
         <v>824</v>
       </c>
       <c r="C22" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A22</f>
         <v>41811040</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -39854,7 +39854,7 @@
         <v>2128</v>
       </c>
       <c r="C23" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A23</f>
         <v>41811090</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -39889,7 +39889,7 @@
         <v>826</v>
       </c>
       <c r="C24" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A24</f>
         <v>41811110</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -39924,7 +39924,7 @@
         <v>2131</v>
       </c>
       <c r="C25" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A25</f>
         <v>41811120</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -39959,7 +39959,7 @@
         <v>2134</v>
       </c>
       <c r="C26" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A26</f>
         <v>41811121</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -39994,7 +39994,7 @@
         <v>831</v>
       </c>
       <c r="C27" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A27</f>
         <v>41811130</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -40029,7 +40029,7 @@
         <v>972</v>
       </c>
       <c r="C28" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A28</f>
         <v>41813051</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -40064,7 +40064,7 @@
         <v>833</v>
       </c>
       <c r="C29" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A29</f>
         <v>41820000</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -40101,7 +40101,7 @@
         <v>839</v>
       </c>
       <c r="C30" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A30</f>
         <v>41820003</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -40138,7 +40138,7 @@
         <v>2136</v>
       </c>
       <c r="C31" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A31</f>
         <v>41820004</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -40173,7 +40173,7 @@
         <v>841</v>
       </c>
       <c r="C32" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A32</f>
         <v>41820030</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -40210,7 +40210,7 @@
         <v>847</v>
       </c>
       <c r="C33" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A33</f>
         <v>41820031</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -40247,7 +40247,7 @@
         <v>849</v>
       </c>
       <c r="C34" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A34</f>
         <v>41820033</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -40284,7 +40284,7 @@
         <v>851</v>
       </c>
       <c r="C35" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A35</f>
         <v>41820034</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -40321,7 +40321,7 @@
         <v>853</v>
       </c>
       <c r="C36" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A36</f>
         <v>41820059</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -40358,7 +40358,7 @@
         <v>858</v>
       </c>
       <c r="C37" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>$C$3&amp;A37</f>
         <v>41820060</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -40395,7 +40395,7 @@
         <v>860</v>
       </c>
       <c r="C38" s="4" t="str">
-        <f t="shared" ref="C38:C69" si="1">$C$3&amp;A38</f>
+        <f>$C$3&amp;A38</f>
         <v>41820061</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -40432,7 +40432,7 @@
         <v>865</v>
       </c>
       <c r="C39" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A39</f>
         <v>41820062</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -40469,7 +40469,7 @@
         <v>867</v>
       </c>
       <c r="C40" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A40</f>
         <v>41820063</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -40506,7 +40506,7 @@
         <v>869</v>
       </c>
       <c r="C41" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A41</f>
         <v>41820064</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -40543,7 +40543,7 @@
         <v>871</v>
       </c>
       <c r="C42" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A42</f>
         <v>41820065</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -40580,7 +40580,7 @@
         <v>873</v>
       </c>
       <c r="C43" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A43</f>
         <v>41820067</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -40617,7 +40617,7 @@
         <v>875</v>
       </c>
       <c r="C44" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A44</f>
         <v>41820068</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -40654,7 +40654,7 @@
         <v>880</v>
       </c>
       <c r="C45" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A45</f>
         <v>41820089</v>
       </c>
       <c r="D45" s="3" t="s">
@@ -40691,7 +40691,7 @@
         <v>882</v>
       </c>
       <c r="C46" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A46</f>
         <v>41820900</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -40728,7 +40728,7 @@
         <v>885</v>
       </c>
       <c r="C47" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A47</f>
         <v>41823590</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -40765,7 +40765,7 @@
         <v>2255</v>
       </c>
       <c r="C48" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A48</f>
         <v>41824951</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -40800,7 +40800,7 @@
         <v>2258</v>
       </c>
       <c r="C49" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A49</f>
         <v>41824970</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -40835,7 +40835,7 @@
         <v>887</v>
       </c>
       <c r="C50" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A50</f>
         <v>41830100</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -40870,7 +40870,7 @@
         <v>891</v>
       </c>
       <c r="C51" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A51</f>
         <v>41830102</v>
       </c>
       <c r="D51" s="3" t="s">
@@ -40905,7 +40905,7 @@
         <v>896</v>
       </c>
       <c r="C52" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A52</f>
         <v>41830130</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -40940,7 +40940,7 @@
         <v>898</v>
       </c>
       <c r="C53" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A53</f>
         <v>41830131</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -40975,7 +40975,7 @@
         <v>900</v>
       </c>
       <c r="C54" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A54</f>
         <v>41830133</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -41010,7 +41010,7 @@
         <v>902</v>
       </c>
       <c r="C55" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A55</f>
         <v>41830134</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -41045,7 +41045,7 @@
         <v>904</v>
       </c>
       <c r="C56" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A56</f>
         <v>41830159</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -41080,7 +41080,7 @@
         <v>909</v>
       </c>
       <c r="C57" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A57</f>
         <v>41830161</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -41115,7 +41115,7 @@
         <v>914</v>
       </c>
       <c r="C58" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A58</f>
         <v>41830164</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -41150,7 +41150,7 @@
         <v>916</v>
       </c>
       <c r="C59" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A59</f>
         <v>41830166</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -41185,7 +41185,7 @@
         <v>919</v>
       </c>
       <c r="C60" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A60</f>
         <v>41830167</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -41220,7 +41220,7 @@
         <v>921</v>
       </c>
       <c r="C61" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A61</f>
         <v>41830189</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -41255,7 +41255,7 @@
         <v>926</v>
       </c>
       <c r="C62" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A62</f>
         <v>41840000</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -41290,7 +41290,7 @@
         <v>930</v>
       </c>
       <c r="C63" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A63</f>
         <v>41840001</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -41325,7 +41325,7 @@
         <v>932</v>
       </c>
       <c r="C64" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A64</f>
         <v>41840004</v>
       </c>
       <c r="D64" s="3" t="s">
@@ -41360,7 +41360,7 @@
         <v>934</v>
       </c>
       <c r="C65" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A65</f>
         <v>41840031</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -41395,7 +41395,7 @@
         <v>936</v>
       </c>
       <c r="C66" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A66</f>
         <v>41840032</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -41430,7 +41430,7 @@
         <v>938</v>
       </c>
       <c r="C67" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A67</f>
         <v>41840033</v>
       </c>
       <c r="D67" s="3" t="s">
@@ -41465,7 +41465,7 @@
         <v>940</v>
       </c>
       <c r="C68" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A68</f>
         <v>41840034</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -41500,7 +41500,7 @@
         <v>942</v>
       </c>
       <c r="C69" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>$C$3&amp;A69</f>
         <v>41840035</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -41535,7 +41535,7 @@
         <v>944</v>
       </c>
       <c r="C70" s="4" t="str">
-        <f t="shared" ref="C70:C90" si="2">$C$3&amp;A70</f>
+        <f>$C$3&amp;A70</f>
         <v>41840037</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -41570,7 +41570,7 @@
         <v>946</v>
       </c>
       <c r="C71" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A71</f>
         <v>41840101</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -41605,7 +41605,7 @@
         <v>948</v>
       </c>
       <c r="C72" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A72</f>
         <v>41840102</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -41640,7 +41640,7 @@
         <v>950</v>
       </c>
       <c r="C73" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A73</f>
         <v>41840200</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -41677,7 +41677,7 @@
         <v>955</v>
       </c>
       <c r="C74" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A74</f>
         <v>41840201</v>
       </c>
       <c r="D74" s="3" t="s">
@@ -41714,7 +41714,7 @@
         <v>958</v>
       </c>
       <c r="C75" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A75</f>
         <v>41840202</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -41751,7 +41751,7 @@
         <v>960</v>
       </c>
       <c r="C76" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A76</f>
         <v>41840203</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -41788,7 +41788,7 @@
         <v>962</v>
       </c>
       <c r="C77" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A77</f>
         <v>41840204</v>
       </c>
       <c r="D77" s="3" t="s">
@@ -41825,7 +41825,7 @@
         <v>964</v>
       </c>
       <c r="C78" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A78</f>
         <v>41840205</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -41862,7 +41862,7 @@
         <v>966</v>
       </c>
       <c r="C79" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A79</f>
         <v>41840206</v>
       </c>
       <c r="D79" s="3" t="s">
@@ -41899,7 +41899,7 @@
         <v>968</v>
       </c>
       <c r="C80" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A80</f>
         <v>41841000</v>
       </c>
       <c r="D80" s="3" t="s">
@@ -41934,7 +41934,7 @@
         <v>2191</v>
       </c>
       <c r="C81" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A81</f>
         <v>41841300</v>
       </c>
       <c r="D81" s="3" t="s">
@@ -41969,7 +41969,7 @@
         <v>2194</v>
       </c>
       <c r="C82" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A82</f>
         <v>41841400</v>
       </c>
       <c r="D82" s="3" t="s">
@@ -42004,7 +42004,7 @@
         <v>970</v>
       </c>
       <c r="C83" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A83</f>
         <v>41846000</v>
       </c>
       <c r="D83" s="3" t="s">
@@ -42039,7 +42039,7 @@
         <v>2139</v>
       </c>
       <c r="C84" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A84</f>
         <v>41860000</v>
       </c>
       <c r="D84" s="3" t="s">
@@ -42074,7 +42074,7 @@
         <v>976</v>
       </c>
       <c r="C85" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A85</f>
         <v>41863000</v>
       </c>
       <c r="D85" s="3" t="s">
@@ -42109,7 +42109,7 @@
         <v>983</v>
       </c>
       <c r="C86" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A86</f>
         <v>41863100</v>
       </c>
       <c r="D86" s="3" t="s">
@@ -42146,7 +42146,7 @@
         <v>989</v>
       </c>
       <c r="C87" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A87</f>
         <v>41863310</v>
       </c>
       <c r="D87" s="3" t="s">
@@ -42181,7 +42181,7 @@
         <v>992</v>
       </c>
       <c r="C88" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A88</f>
         <v>41863331</v>
       </c>
       <c r="D88" s="3" t="s">
@@ -42216,7 +42216,7 @@
         <v>994</v>
       </c>
       <c r="C89" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A89</f>
         <v>41863440</v>
       </c>
       <c r="D89" s="3" t="s">
@@ -42251,7 +42251,7 @@
         <v>1003</v>
       </c>
       <c r="C90" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f>$C$3&amp;A90</f>
         <v>41870000</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -42294,7 +42294,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K90" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A5:K90" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:K91">
+      <sortCondition ref="A5:A90"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A2:K2"/>
   </mergeCells>
@@ -42321,7 +42325,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G114"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -45021,7 +45025,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F140"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -47440,7 +47444,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>1425</v>
       </c>
@@ -47886,7 +47890,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="150" customWidth="1"/>
@@ -48135,7 +48139,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E708"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="52" customWidth="1"/>
@@ -59012,4 +59016,10 @@
     <oddFooter>&amp;C&amp;8 &amp;A – Seite &amp;P von &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{ea60d57e-af5b-4752-ac57-3e4f28ca11dc}" enabled="1" method="Standard" siteId="{36da45f1-dd2c-4d1f-af13-5abe46b99921}" removed="0"/>
+</clbl:labelList>
 </file>